--- a/wb_parser/output/excel/wildberries.xlsx
+++ b/wb_parser/output/excel/wildberries.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:48</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -537,34 +537,34 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 5G 12+256GB Galaxy Black</t>
+          <t>Смартфон POVA 6 Neo 8+128GB Black</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17</v>
+        <v>1754</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29840</v>
+        <v>11243</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>39990</v>
+        <v>14990</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>25</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/404291033/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/232387193/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:48</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -574,34 +574,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 5G 8+256GB Glacier White</t>
+          <t>Смартфон POVA 6 Neo 8+128GB Green</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25112</v>
+        <v>11243</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>36990</v>
+        <v>14990</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/439858674/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/242140633/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:48</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -611,34 +611,34 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 5G 12+256GB Emerald Lake Green</t>
+          <t>Смартфон SPARK 30 Pro 8+128GB Obsidian Edge</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
+        <v>927</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>29920</v>
+        <v>11357</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>39990</v>
+        <v>14490</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/404291032/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/273212866/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:48</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -648,34 +648,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 8+256GB Glacier White</t>
+          <t>Смартфон SPARK 30 Pro 8+256GB Obsidian Edge</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>605</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>23108</v>
+        <v>12936</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27990</v>
+        <v>15990</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/404281464/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/300338885/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -685,34 +685,34 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30 Pro 8+128GB Obsidian Edge</t>
+          <t>Смартфон SPARK 30C 6+128GB Titanium Gold</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>926</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>11357</v>
+        <v>8419</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>14490</v>
+        <v>9990</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/273212866/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/391577739/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -722,34 +722,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 8+256GB Galaxy Black</t>
+          <t>Смартфон SPARK 30C 6+128GB Orbit White</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>23108</v>
+        <v>8419</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>27990</v>
+        <v>9990</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/404281463/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/342625086/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -759,34 +759,34 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Pova 7 5G 256Gb 8Gb черный</t>
+          <t>Смартфон SPARK 30C 4+128GB Titanium Gold</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>21120</v>
+        <v>7576</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>24559</v>
+        <v>8990</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/486674401/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/370287561/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -796,34 +796,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30 Pro 8+256GB Obsidian Edge</t>
+          <t>Смартфон SPARK 30C 4+128GB Orbit White</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>605</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>12936</v>
+        <v>7576</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15990</v>
+        <v>8990</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/300338885/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/370284976/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:31</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -833,34 +833,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Pro 5G 12+256GB Glacier White</t>
+          <t>Смартфон Spark 30C 4 128Гб</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>29920</v>
+        <v>7239</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>39990</v>
+        <v>8590</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/439864565/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/444620963/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -870,34 +870,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo 8 256GB (LI6) Черный</t>
+          <t>Смартфон Spark 30C 4 128Гб</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>237</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>14875</v>
+        <v>7239</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>17651</v>
+        <v>8590</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/241712203/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/444620964/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -907,34 +907,34 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Pova 6 Pro 5G 12 256Gb (LI9) Серый</t>
+          <t>Смартфон SPARK 30 8+256GB Astral Ice</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>22998</v>
+        <v>11200</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>26743</v>
+        <v>13990</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/266870501/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/342625065/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -944,34 +944,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo 8+128GB Black</t>
+          <t>SPARK 30 Pro 8+128GB Arctic Glow</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1750</v>
+        <v>82</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>11243</v>
+        <v>11362</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>14990</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/232387193/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/316806389/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -981,34 +981,34 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 5G 8 256GB (CM7) Зеленый</t>
+          <t>Смартфон Camon 40 Pro 8 256 ГБ Черный</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24662</v>
+        <v>25990</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>28025</v>
+        <v>30221</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/415395536/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/413897461/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1018,34 +1018,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo 8+128GB Green</t>
+          <t>Смартфон SPARK 30C 6+128GB Magic Skin Green</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>674</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>11243</v>
+        <v>8419</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14990</v>
+        <v>9990</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/242140633/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/391577737/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1055,34 +1055,34 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30C 6 128 ГБ белый</t>
+          <t>Смартфон SPARK 30C 6+128GB Orbit Black</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7681</v>
+        <v>8419</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>9114</v>
+        <v>9990</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/332380820/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/391577738/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1092,34 +1092,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 5G 12 256 ГБ зеленый</t>
+          <t>Смартфон Pova 7 5G 256Gb 8Gb черный</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>29839</v>
+        <v>21120</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>34697</v>
+        <v>24559</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/423428007/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/486674401/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:49</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1129,34 +1129,34 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 5G 8 256 ГБ зеленый</t>
+          <t>Смартфон Pova 7 Neo 256 ГБ (Черный)</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>24572</v>
+        <v>16331</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>27003</v>
+        <v>18990</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/423428008/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/482944503/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1166,34 +1166,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 8+256GB Meteorite Grey</t>
+          <t>Смартфон Pova 7 Neo 256 ГБ (Серебристый)</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>17148</v>
+        <v>16331</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20990</v>
+        <v>18990</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/383656364/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/482944504/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1203,34 +1203,34 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30 5G 6 128 ГБ черный</t>
+          <t>SPARK 30C 4+128GB</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>10100</v>
+        <v>6719</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>11986</v>
+        <v>13990</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/269891778/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805205/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1240,34 +1240,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30C 4 128Гб</t>
+          <t>SPARK 30C 4+128GB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7239</v>
+        <v>6719</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>8590</v>
+        <v>13990</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/444620963/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805206/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1277,34 +1277,34 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30C 4 128Гб</t>
+          <t>SPARK 30C 6+128GB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>7239</v>
+        <v>7452</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8590</v>
+        <v>14990</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/444620964/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805208/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 8+256GB Comet Green</t>
+          <t>SPARK 30C 4+128GB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>17148</v>
+        <v>6719</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20990</v>
+        <v>13990</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/383656363/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805207/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:32</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1351,34 +1351,34 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30 8 128 ГБ белый</t>
+          <t>Смартфон POVA 7 Neo 8 128 ГБ серебристый</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>8419</v>
+        <v>16489</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>9990</v>
+        <v>19174</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/346358647/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473404693/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1388,34 +1388,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 12+256GB Meteorite Grey</t>
+          <t>Смартфон POVA 7 Neo 8 256 ГБ черный</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>19599</v>
+        <v>18373</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23990</v>
+        <v>21364</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/383650147/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473404696/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1425,34 +1425,34 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30 8+256GB Astral Ice</t>
+          <t>Смартфон POVA 7 Neo 8 256 ГБ серебристый</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>11200</v>
+        <v>18373</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>13990</v>
+        <v>21364</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/342625065/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473404695/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1462,34 +1462,34 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8+128GB Geek Black</t>
+          <t>SPARK Go 1 3+64GB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>16831</v>
+        <v>4445</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>21990</v>
+        <v>10990</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460897168/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805213/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1499,34 +1499,34 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256 ГБ черный</t>
+          <t>SPARK Go 1 3+64GB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19780</v>
+        <v>4445</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23000</v>
+        <v>10990</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/399115482/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805215/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 12+256GB Comet Green</t>
+          <t>Смартфон POVA 7 Neo 8 256 ГБ бежевый</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>19599</v>
+        <v>18373</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23990</v>
+        <v>21364</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/383588355/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/473404692/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1573,34 +1573,34 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30 Pro 8+128GB Arctic Glow</t>
+          <t>Смартфон Spark 40 Pro 8 256Gb Black</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>11362</v>
+        <v>18481</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>14990</v>
+        <v>21490</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/316806389/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/476434778/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:50</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8+128GB Magic Silver</t>
+          <t>SPARK Go 1 3+64GB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>16831</v>
+        <v>4445</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21990</v>
+        <v>10990</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460900775/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/456805216/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1647,34 +1647,34 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8+256GB Magic Silver</t>
+          <t>Смартфон CAMON 40 Premier 5G 12+256GB Galaxy Black</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>18774</v>
+        <v>44926</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23990</v>
+        <v>54990</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460900777/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/403272767/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1684,71 +1684,71 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8+256GB Hyper Titanium</t>
+          <t>Смартфон CAMON 40 Premier 5G 12+256GB Emerald Lake Green</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>18774</v>
+        <v>44926</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23990</v>
+        <v>54990</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460900779/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/403272766/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TECNO</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256 ГБ белый</t>
+          <t>Смартфон POVA 6 Neo LI6 8 128 ГБ черный 6.8"</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>19</v>
+        <v>819</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19780</v>
+        <v>11950</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23000</v>
+        <v>19971</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/397578385/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/233972247/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1758,34 +1758,34 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8+256GB Geek Black</t>
+          <t>Смартфон POVA 7 Neo 8+128GB Geek Black</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>18774</v>
+        <v>16831</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23990</v>
+        <v>21990</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/460900776/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460897168/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 12 256 ГБ белый</t>
+          <t>Смартфон POVA 7 Neo 8+128GB Magic Silver</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1805,24 +1805,24 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>20888</v>
+        <v>16831</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>24289</v>
+        <v>21990</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/446606436/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460900775/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1832,34 +1832,34 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 5G 8 256 ГБ белый</t>
+          <t>Смартфон POVA 7 Neo 8+256GB Magic Silver</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>23222</v>
+        <v>18774</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>27003</v>
+        <v>23990</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/455045341/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460900777/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:33</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1869,71 +1869,71 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 12 256 ГБ черный</t>
+          <t>Смартфон POVA 7 Neo 8+256GB Hyper Titanium</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>20888</v>
+        <v>18774</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>24289</v>
+        <v>23990</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/446606438/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460900779/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TECNO</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 12 256 ГБ зеленый</t>
+          <t>Смартфон POVA 6 Neo LI6 8 128 ГБ зеленый</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>20888</v>
+        <v>15489</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>24289</v>
+        <v>19858</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/446606439/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/268695847/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1943,71 +1943,71 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8 128GB (LJ6) Черный</t>
+          <t>Смартфон POVA 7 Neo 8+256GB Geek Black</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>16082</v>
+        <v>18774</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>18700</v>
+        <v>23990</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/445637520/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/460900776/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TECNO</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Pova 7 Neo 256 ГБ (Серебристый)</t>
+          <t>Смартфон POVA 6 Neo LI6 8 256 ГБ черный 6.8"</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>16331</v>
+        <v>18589</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>18990</v>
+        <v>20887</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/482944504/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/232443172/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Pova 7 Neo 256 ГБ (Черный)</t>
+          <t>Смартфон Camon 20 8+256GB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2027,24 +2027,24 @@
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>16331</v>
+        <v>8721</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>18990</v>
+        <v>19900</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/482944503/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/413430544/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:51</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2054,34 +2054,34 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30C 4+128GB</t>
+          <t>Смартфон Camon 20 8+256GB</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>6719</v>
+        <v>8721</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13990</v>
+        <v>19900</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805205/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/413430543/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2091,34 +2091,34 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Premier 5G 12 256GB (CM8) Черный</t>
+          <t>Смартфон Camon 20 8+256GB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>40763</v>
+        <v>8721</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>47399</v>
+        <v>19900</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/392057793/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/413683612/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2128,34 +2128,34 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30C 6+128GB</t>
+          <t>SPARK Go 1 3+64GB + Смарт часы + Наушники</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>7452</v>
+        <v>8494</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>14990</v>
+        <v>21000</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805208/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/277281689/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30C 4+128GB</t>
+          <t>Смартфон Camon 20 8+256GB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2175,24 +2175,24 @@
         <v>0</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>6719</v>
+        <v>8721</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>13990</v>
+        <v>19900</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805206/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/413683611/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Premier 5G 12 256 ГБ зеленый</t>
+          <t>Смартфон Camon 40 8 256 Sandy Titanium</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2212,24 +2212,24 @@
         <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>44925</v>
+        <v>17826</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>52239</v>
+        <v>20729</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/398376336/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/482605883/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2239,34 +2239,34 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30C 4+128GB</t>
+          <t>Смартфон POP 7+ 2 64 ГБ + Смарт часы + Наушники</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>6719</v>
+        <v>8191</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>13990</v>
+        <v>21600</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805207/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/259297313/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2276,34 +2276,34 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Premier 5G 12 256 ГБ черный</t>
+          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>44925</v>
+        <v>5716</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>52239</v>
+        <v>23333</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/398388979/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488638614/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256 ГБ титановый</t>
+          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2323,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>19780</v>
+        <v>5716</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>23000</v>
+        <v>23333</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/474374731/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488638613/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:34</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2350,34 +2350,34 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 8 256GB (CM6) Песочный Титан</t>
+          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>20812</v>
+        <v>5716</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>24200</v>
+        <v>23333</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/465609493/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488613779/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2387,34 +2387,34 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256 ГБ зеленый</t>
+          <t>Смартфон Spark GO 2024 3+64GB + СМАРТ ЧАСЫ + НАУШНИКИ</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>19186</v>
+        <v>8873</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>22310</v>
+        <v>23400</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/399115481/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/208821758/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2424,34 +2424,34 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 8 256 ГБ белый</t>
+          <t>Смартфон Phantom V Flip2 5G Ростест 8 256 ГБ, серый</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>23108</v>
+        <v>49043</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>26870</v>
+        <v>53894</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/399059330/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/320500846/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2461,34 +2461,34 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 8 256 ГБ черный</t>
+          <t>Смартфон POVA 6 12 256GB серый РОСТЕСТ</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>23108</v>
+        <v>18017</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>26870</v>
+        <v>20950</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/399082702/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/374802489/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2498,34 +2498,34 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SPARK Go 1 3+64GB</t>
+          <t>Смартфон POVA 6 12 256GB зеленый РОСТЕСТ</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>4445</v>
+        <v>18017</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10990</v>
+        <v>20950</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805213/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/402782812/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:52</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2535,34 +2535,34 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SPARK Go 1 3+64GB</t>
+          <t>Смартфон POVA 6 Pro 5G 12 256GB РОСТЕСТ</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>4445</v>
+        <v>21758</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>10990</v>
+        <v>25300</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805215/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/401834390/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2572,34 +2572,34 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 12 256GB (CM5) Песочный Титан</t>
+          <t>CAMON 30S +Смарт часы + Наушники</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>19780</v>
+        <v>18163</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>23000</v>
+        <v>44000</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/465584800/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/366243037/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SPARK Go 1 3+64GB</t>
+          <t>Смартфон Phantom V Flip2 5G Ростест 8 256 ГБ, зеленый</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>4445</v>
+        <v>49043</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10990</v>
+        <v>53894</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/456805216/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/320502286/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2646,34 +2646,34 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256GB (CM5) Песочный Титан</t>
+          <t>Phantom V Fold 2 5G 12 512GB темно-зеленый + V Pen</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>17999</v>
+        <v>84185</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>20930</v>
+        <v>92512</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/465579527/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/395985483/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2683,34 +2683,34 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 8 256 ГБ титановый</t>
+          <t>SPARK 30 Pro 8+256GB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>23108</v>
+        <v>11120</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>26870</v>
+        <v>23990</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/475986478/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/323100649/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2720,34 +2720,34 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8 128 ГБ серебристый</t>
+          <t>SPARK 30 Pro 8+256GB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>1092</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>16489</v>
+        <v>11120</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>19174</v>
+        <v>23990</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473404693/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/342398658/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2757,34 +2757,34 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8 256 ГБ черный</t>
+          <t>Смартфон SPARK 30C 256+8GB Orbit Black</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>4</v>
+        <v>696</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>18373</v>
+        <v>9700</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>21364</v>
+        <v>11990</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473404696/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/265773358/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2794,34 +2794,34 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8 256 ГБ серебристый</t>
+          <t>Смартфон SPARK Go 1 4+128GB Black</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>1084</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>18373</v>
+        <v>5890</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>21364</v>
+        <v>6990</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473404695/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/263891743/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:35</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2831,71 +2831,71 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 7 Neo 8 256 ГБ бежевый</t>
+          <t>SPARK 30C 8+256GB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>18373</v>
+        <v>8945</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>21364</v>
+        <v>17990</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/473404692/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/440511834/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>TECNO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo LI6 8 128 ГБ черный 6.8"</t>
+          <t>Смартфон CAMON 30S 6+128GB Dawn Gold</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>818</v>
+        <v>264</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>11950</v>
+        <v>11370</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>19971</v>
+        <v>17990</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/233972247/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/370270488/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2905,34 +2905,34 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 Pro 8 256 ГБ Черный</t>
+          <t>Смартфон SPARK 30 5G 6+128GB Black</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>6</v>
+        <v>628</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>25990</v>
+        <v>8538</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>30221</v>
+        <v>12990</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/413897461/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/263891739/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2942,108 +2942,108 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Premier 5G 12+256GB Galaxy Black</t>
+          <t>POVA 6 Neo 8+128GB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>6</v>
+        <v>571</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>44926</v>
+        <v>11363</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>54990</v>
+        <v>18990</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/403272767/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/323100643/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:53</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>TECNO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo LI6 8 128 ГБ зеленый</t>
+          <t>Смартфон SPARK Go 1 3+64GB Gold</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>15489</v>
+        <v>4626</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>19858</v>
+        <v>5490</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/268695847/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/344001545/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>TECNO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Neo LI6 8 256 ГБ черный 6.8"</t>
+          <t>Смартфон Spark 30C 6,67" 6ГБ 128ГБ белый</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>18589</v>
+        <v>9850</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>20887</v>
+        <v>11689</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/232443172/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/326230422/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3053,34 +3053,34 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 40 Premier 5G 12+256GB Emerald Lake Green</t>
+          <t>Смартфон SPARK 30C 256+8GB Titanium Gold</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>44926</v>
+        <v>9700</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>54990</v>
+        <v>11990</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/403272766/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/366775999/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3090,34 +3090,34 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 20 8+256GB</t>
+          <t>POVA 6 Neo 8+128GB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>8721</v>
+        <v>11363</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>19900</v>
+        <v>18990</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/413430544/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/323100645/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 20 8+256GB</t>
+          <t>Смартфон Spark 30C 6,67" 4ГБ 128ГБ белый</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -3137,24 +3137,24 @@
         <v>0</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>8721</v>
+        <v>7618</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>19900</v>
+        <v>9040</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/413430543/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/275414101/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 20 8+256GB</t>
+          <t>Смартфон Spark 30C 6,67" 4ГБ 128ГБ зеленый</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3174,24 +3174,24 @@
         <v>0</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>8721</v>
+        <v>7576</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>19900</v>
+        <v>8990</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/413683612/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/326230439/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3201,34 +3201,34 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>SPARK Go 1 3+64GB + Смарт часы + Наушники</t>
+          <t>Смартфон SPARK 30C 6+128GB Magic Skin Green</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>8494</v>
+        <v>7577</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>21000</v>
+        <v>9990</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/277281689/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/296080209/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 20 8+256GB</t>
+          <t>Смартфон Spark 10 4 128GB Meta White</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -3248,24 +3248,24 @@
         <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>8721</v>
+        <v>11269</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>19900</v>
+        <v>11499</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/413683611/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371668676/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3275,34 +3275,34 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Camon 40 8 256 Sandy Titanium</t>
+          <t>Смартфон SPARK 30C 6+128GB Orbit White</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>17826</v>
+        <v>7577</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20729</v>
+        <v>9990</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/482605883/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/263891741/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:36</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3312,34 +3312,34 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POP 7+ 2 64 ГБ + Смарт часы + Наушники</t>
+          <t>Смартфон SPARK 30 8+256GB Black</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>198</v>
+        <v>391</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>8191</v>
+        <v>9524</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>21600</v>
+        <v>12990</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/259297313/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/273212864/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3349,34 +3349,34 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
+          <t>Смартфон SPARK 30C 4+128GB Magic Skin Green</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>5716</v>
+        <v>6818</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>23333</v>
+        <v>8990</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488638614/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/313640598/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
+          <t>Смартфон Spark 20C 4 256GB Mystery White</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -3396,24 +3396,24 @@
         <v>0</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>5716</v>
+        <v>12503</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>23333</v>
+        <v>12759</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488613779/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371667100/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:54</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3423,34 +3423,34 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30 Pro, 12+256 ГБ，5800 мАч</t>
+          <t>Смартфон SPARK 30C 128+4 ГБ золотистый</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>5716</v>
+        <v>7575</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>23333</v>
+        <v>13830</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488638613/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/437135647/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3460,71 +3460,71 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark GO 2024 3+64GB + СМАРТ ЧАСЫ + НАУШНИКИ</t>
+          <t>Смартфон Spark 30 8+128GB Astral Ice</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>8873</v>
+        <v>10328</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>23400</v>
+        <v>10539</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/208821758/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371640554/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TECNO</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Phantom V Flip2 5G Ростест 8 256 ГБ, серый</t>
+          <t>Смартфон POP 7 2 64Gb Black + Часы</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>49043</v>
+        <v>8843</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>53894</v>
+        <v>11659</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/320500846/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/333968267/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3534,34 +3534,34 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 12 256GB серый РОСТЕСТ</t>
+          <t>Смартфон SPARK 30C 4+128GB Orbit White</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>18017</v>
+        <v>6818</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>20950</v>
+        <v>8990</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/374802489/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/265773349/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3571,34 +3571,34 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 12 256GB зеленый РОСТЕСТ</t>
+          <t>Смартфон Spark 30C 6,67" 8ГБ 256ГБ белый</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>18017</v>
+        <v>11822</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>20950</v>
+        <v>14029</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/402782812/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/275414072/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3608,34 +3608,34 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Смартфон POVA 6 Pro 5G 12 256GB РОСТЕСТ</t>
+          <t>Смартфон SPARK 30 8+128GB White</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>21758</v>
+        <v>7501</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>25300</v>
+        <v>10990</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/401834390/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/296082027/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -3645,34 +3645,34 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CAMON 30S +Смарт часы + Наушники</t>
+          <t>Смартфон Spark 20 8+128GB черный</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>18163</v>
+        <v>13140</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>44000</v>
+        <v>13409</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/366243037/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371667710/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -3682,34 +3682,34 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Phantom V Flip2 5G Ростест 8 256 ГБ, зеленый</t>
+          <t>Смартфон Spark 30C 6,67" 6ГБ 128ГБ черный</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>49043</v>
+        <v>9008</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>53894</v>
+        <v>10689</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/320502286/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/326230418/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3719,34 +3719,34 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Phantom V Fold 2 5G 12 512GB темно-зеленый + V Pen</t>
+          <t>Смартфон Spark 20 8 128GB Magic Skin Blue</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>84185</v>
+        <v>13140</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>92512</v>
+        <v>13409</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/395985483/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371667711/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3756,34 +3756,34 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30 Pro 8+256GB</t>
+          <t>Смартфон SPARK 30 8+256GB White</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>420</v>
+        <v>276</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>11120</v>
+        <v>9524</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>23990</v>
+        <v>12990</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/323100649/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/296082787/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:37</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3793,34 +3793,34 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30 Pro 8+256GB</t>
+          <t>Смартфон POVA 6 Neo 8 256GB (LI6) Черный</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1082</v>
+        <v>237</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>11120</v>
+        <v>14875</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>23990</v>
+        <v>17651</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/342398658/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/241712203/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3830,34 +3830,34 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30C 256+8GB Orbit Black</t>
+          <t>Смартфон SPARK Go 1 4+128GB White</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>696</v>
+        <v>470</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>9700</v>
+        <v>5890</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>11990</v>
+        <v>6990</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/265773358/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/263891742/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3867,34 +3867,34 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>SPARK 30C 8+256GB</t>
+          <t>Смартфон POVA 6 Neo 8 128 ГБ черный</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>8945</v>
+        <v>13188</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>17990</v>
+        <v>19986</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/440511834/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/436948726/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3904,34 +3904,34 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK Go 1 4+128GB Black</t>
+          <t>Смартфон Spark 30 256Gb 8Gb серебристый</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>5890</v>
+        <v>11158</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>6990</v>
+        <v>13240</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/263891743/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/320846390/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:55</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Смартфон CAMON 30S 6+128GB Dawn Gold</t>
+          <t>Смартфон Spark 30 256Gb 8Gb black</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>11370</v>
+        <v>11158</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>17990</v>
+        <v>13240</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/370270488/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/275414070/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3978,34 +3978,34 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30 5G 6+128GB Black</t>
+          <t>Смартфон Spark 30 128Gb 8Gb серебристый</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>8538</v>
+        <v>9358</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>12990</v>
+        <v>11104</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/263891739/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/320846393/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4015,34 +4015,34 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>POVA 6 Neo 8+128GB</t>
+          <t>Смартфон Spark 30C 256Gb 8Gb золотистый</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>11363</v>
+        <v>10146</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>18990</v>
+        <v>12040</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/323100643/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/376553301/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4052,34 +4052,34 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>POVA 6 Neo 8+128GB</t>
+          <t>Смартфон Spark 30C 8 256GB Magic Skin Green</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>11363</v>
+        <v>11043</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>18990</v>
+        <v>11269</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/323100645/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371639911/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4089,34 +4089,34 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK Go 1 3+64GB Gold</t>
+          <t>SPARK 30 8+256GB</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>4626</v>
+        <v>9418</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>5490</v>
+        <v>25990</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/344001545/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/348341507/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Смартфон Spark 30C 6,67" 6ГБ 128ГБ белый</t>
+          <t>Смартфон Spark 30 8+256GB Astral Ice</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -4136,24 +4136,24 @@
         <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>9850</v>
+        <v>11700</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>11689</v>
+        <v>11939</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/326230422/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/371641119/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07 12:12:38</t>
+          <t>2025-08-07 15:05:56</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4163,27 +4163,27 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Смартфон SPARK 30C 256+8GB Titanium Gold</t>
+          <t>SPARK 30 5G 6+128GB</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>57</v>
+        <v>194</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>9700</v>
+        <v>9282</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>11990</v>
+        <v>18990</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/366775999/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/323100660/detail.aspx</t>
         </is>
       </c>
     </row>
